--- a/etc/hebrew/pronouns.xlsx
+++ b/etc/hebrew/pronouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -785,6 +785,48 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>he; it</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>הוּא</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>pronoun</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>we</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>אֲנַחְנוּ</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>pronoun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/pronouns.xlsx
+++ b/etc/hebrew/pronouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -827,6 +827,48 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>מִישֶׁהוּ</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>pronoun</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>me (direct object)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>אוֹתִי</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>object pronoun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
